--- a/_ForDRA/BVSimulationFiles/68.xlsx
+++ b/_ForDRA/BVSimulationFiles/68.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.001628664495114006</v>
+        <v>0.03257328990228012</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001622820387002321</v>
+        <v>0.03245640774004642</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001616996104450127</v>
+        <v>0.03233992208900254</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00161119158645256</v>
+        <v>0.0322238317290512</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001605406772156369</v>
+        <v>0.03210813544312738</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001599641600859757</v>
+        <v>0.03199283201719514</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001593896012012244</v>
+        <v>0.03187792024024488</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001588169945214509</v>
+        <v>0.03176339890429018</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001582463340218243</v>
+        <v>0.03164926680436486</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001576776136925994</v>
+        <v>0.03153552273851988</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001571108275391009</v>
+        <v>0.03142216550782018</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001565459695817083</v>
+        <v>0.03130919391634166</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001559830338558397</v>
+        <v>0.03119660677116794</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00155422014411936</v>
+        <v>0.0310844028823872</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001548629053154447</v>
+        <v>0.03097258106308894</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001543057006468034</v>
+        <v>0.03086114012936068</v>
       </c>
       <c r="R2" t="n">
-        <v>0.00153750394501424</v>
+        <v>0.0307500789002848</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001531969809896755</v>
+        <v>0.0306393961979351</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001526454542368675</v>
+        <v>0.0305290908473735</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001520958083832336</v>
+        <v>0.03041916167664672</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.001628664495114006</v>
+        <v>0.03257328990228012</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001622820387002321</v>
+        <v>0.03245640774004642</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001616996104450127</v>
+        <v>0.03233992208900254</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00161119158645256</v>
+        <v>0.0322238317290512</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001605406772156369</v>
+        <v>0.03210813544312738</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001599641600859757</v>
+        <v>0.03199283201719514</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001593896012012244</v>
+        <v>0.03187792024024488</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001588169945214509</v>
+        <v>0.03176339890429018</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001582463340218243</v>
+        <v>0.03164926680436486</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001576776136925994</v>
+        <v>0.03153552273851988</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001571108275391009</v>
+        <v>0.03142216550782018</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001565459695817083</v>
+        <v>0.03130919391634166</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001559830338558397</v>
+        <v>0.03119660677116794</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00155422014411936</v>
+        <v>0.0310844028823872</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001548629053154447</v>
+        <v>0.03097258106308894</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001543057006468034</v>
+        <v>0.03086114012936068</v>
       </c>
       <c r="R3" t="n">
-        <v>0.00153750394501424</v>
+        <v>0.0307500789002848</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001531969809896755</v>
+        <v>0.0306393961979351</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001526454542368675</v>
+        <v>0.0305290908473735</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001520958083832336</v>
+        <v>0.03041916167664672</v>
       </c>
     </row>
   </sheetData>
